--- a/rcads/data/xls/03_Activities.xlsx
+++ b/rcads/data/xls/03_Activities.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_03_Activities"/>
   </sheets>
   <definedNames>
-    <definedName name="_03_Activities">'_03_Activities'!$A$1:$G$110</definedName>
+    <definedName name="_03_Activities">'_03_Activities'!$A$1:$H$122</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -347,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -386,6 +386,11 @@
           <t>GenEntityID</t>
         </is>
       </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="0">
@@ -505,6 +510,9 @@
       <c r="G6" s="0">
         <v>6</v>
       </c>
+      <c r="H6" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row outlineLevel="0" r="7">
       <c r="A7" s="0">
@@ -555,6 +563,9 @@
       <c r="G8" s="0">
         <v>10</v>
       </c>
+      <c r="H8" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="0">
@@ -702,6 +713,9 @@
       <c r="G14" s="0">
         <v>14</v>
       </c>
+      <c r="H14" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="0">
@@ -1127,6 +1141,9 @@
       <c r="G31" s="0">
         <v>38</v>
       </c>
+      <c r="H31" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0">
@@ -1377,6 +1394,9 @@
       <c r="G41" s="0">
         <v>50</v>
       </c>
+      <c r="H41" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="0">
@@ -1402,6 +1422,9 @@
       <c r="G42" s="0">
         <v>51</v>
       </c>
+      <c r="H42" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="0">
@@ -1527,6 +1550,9 @@
       <c r="G47" s="0">
         <v>60</v>
       </c>
+      <c r="H47" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="0">
@@ -1552,6 +1578,9 @@
       <c r="G48" s="0">
         <v>61</v>
       </c>
+      <c r="H48" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="0">
@@ -2002,6 +2031,9 @@
       <c r="G66" s="0">
         <v>89</v>
       </c>
+      <c r="H66" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="0">
@@ -2202,6 +2234,9 @@
       <c r="G74" s="0">
         <v>99</v>
       </c>
+      <c r="H74" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="0">
@@ -2727,6 +2762,9 @@
       <c r="G95" s="0">
         <v>136</v>
       </c>
+      <c r="H95" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="0">
@@ -2752,6 +2790,9 @@
       <c r="G96" s="0">
         <v>138</v>
       </c>
+      <c r="H96" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="0">
@@ -2777,6 +2818,9 @@
       <c r="G97" s="0">
         <v>140</v>
       </c>
+      <c r="H97" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="0">
@@ -2802,6 +2846,9 @@
       <c r="G98" s="0">
         <v>142</v>
       </c>
+      <c r="H98" s="0">
+        <v>3</v>
+      </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="0">
@@ -3098,6 +3145,306 @@
       </c>
       <c r="G110" s="0">
         <v>159</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="111">
+      <c r="A111" s="0">
+        <v>121</v>
+      </c>
+      <c r="B111" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-Y-IT from RCADS-47-Y-IT and RCADS-25-Y-EN</t>
+        </is>
+      </c>
+      <c r="C111" s="0">
+        <v>51</v>
+      </c>
+      <c r="D111" s="1">
+        <v>46044</v>
+      </c>
+      <c r="E111" s="0">
+        <v>1</v>
+      </c>
+      <c r="F111" s="0">
+        <v>167</v>
+      </c>
+      <c r="G111" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="112">
+      <c r="A112" s="0">
+        <v>122</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-CG-IT from RCADS-47-CG-IT and RCADS-25-CG-EN</t>
+        </is>
+      </c>
+      <c r="C112" s="0">
+        <v>51</v>
+      </c>
+      <c r="D112" s="1">
+        <v>46044</v>
+      </c>
+      <c r="E112" s="0">
+        <v>1</v>
+      </c>
+      <c r="F112" s="0">
+        <v>169</v>
+      </c>
+      <c r="G112" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="113">
+      <c r="A113" s="0">
+        <v>123</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-Y-MR from RCADS-47-Y-EN</t>
+        </is>
+      </c>
+      <c r="C113" s="0">
+        <v>53</v>
+      </c>
+      <c r="D113" s="1">
+        <v>45974</v>
+      </c>
+      <c r="E113" s="0">
+        <v>1</v>
+      </c>
+      <c r="F113" s="0">
+        <v>1</v>
+      </c>
+      <c r="G113" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="114">
+      <c r="A114" s="0">
+        <v>124</v>
+      </c>
+      <c r="B114" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-CG-MR from RCADS-47-CG-EN</t>
+        </is>
+      </c>
+      <c r="C114" s="0">
+        <v>53</v>
+      </c>
+      <c r="D114" s="1">
+        <v>45974</v>
+      </c>
+      <c r="E114" s="0">
+        <v>1</v>
+      </c>
+      <c r="F114" s="0">
+        <v>2</v>
+      </c>
+      <c r="G114" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="115">
+      <c r="A115" s="0">
+        <v>125</v>
+      </c>
+      <c r="B115" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-Y-ZU from RCADS-47-Y-EN</t>
+        </is>
+      </c>
+      <c r="C115" s="0">
+        <v>54</v>
+      </c>
+      <c r="D115" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E115" s="0">
+        <v>1</v>
+      </c>
+      <c r="F115" s="0">
+        <v>1</v>
+      </c>
+      <c r="G115" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="116">
+      <c r="A116" s="0">
+        <v>126</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-CG-ZU from RCADS-47-CG-EN</t>
+        </is>
+      </c>
+      <c r="C116" s="0">
+        <v>54</v>
+      </c>
+      <c r="D116" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E116" s="0">
+        <v>1</v>
+      </c>
+      <c r="F116" s="0">
+        <v>2</v>
+      </c>
+      <c r="G116" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="117">
+      <c r="A117" s="0">
+        <v>127</v>
+      </c>
+      <c r="B117" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-Y-VI from RCADS-47-Y-EN</t>
+        </is>
+      </c>
+      <c r="C117" s="0">
+        <v>55</v>
+      </c>
+      <c r="D117" s="1">
+        <v>45930</v>
+      </c>
+      <c r="E117" s="0">
+        <v>1</v>
+      </c>
+      <c r="F117" s="0">
+        <v>1</v>
+      </c>
+      <c r="G117" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="118">
+      <c r="A118" s="0">
+        <v>128</v>
+      </c>
+      <c r="B118" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-47-CG-VI from RCADS-47-CG-EN</t>
+        </is>
+      </c>
+      <c r="C118" s="0">
+        <v>55</v>
+      </c>
+      <c r="D118" s="1">
+        <v>45930</v>
+      </c>
+      <c r="E118" s="0">
+        <v>1</v>
+      </c>
+      <c r="F118" s="0">
+        <v>2</v>
+      </c>
+      <c r="G118" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="119">
+      <c r="A119" s="0">
+        <v>129</v>
+      </c>
+      <c r="B119" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-Y-ZU from RCADS-47-Y-ZU and RCADS-25-Y-EN</t>
+        </is>
+      </c>
+      <c r="C119" s="0">
+        <v>51</v>
+      </c>
+      <c r="D119" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E119" s="0">
+        <v>1</v>
+      </c>
+      <c r="F119" s="0">
+        <v>178</v>
+      </c>
+      <c r="G119" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="120">
+      <c r="A120" s="0">
+        <v>130</v>
+      </c>
+      <c r="B120" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-CG-ZU from RCADS-47-CG-ZU and RCADS-25-CG-EN</t>
+        </is>
+      </c>
+      <c r="C120" s="0">
+        <v>51</v>
+      </c>
+      <c r="D120" s="1">
+        <v>46041</v>
+      </c>
+      <c r="E120" s="0">
+        <v>1</v>
+      </c>
+      <c r="F120" s="0">
+        <v>179</v>
+      </c>
+      <c r="G120" s="0">
+        <v>177</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="121">
+      <c r="A121" s="0">
+        <v>131</v>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-Y-MR from RCADS-47-Y-MR and RCADS-25-Y-EN</t>
+        </is>
+      </c>
+      <c r="C121" s="0">
+        <v>51</v>
+      </c>
+      <c r="D121" s="1">
+        <v>45974</v>
+      </c>
+      <c r="E121" s="0">
+        <v>1</v>
+      </c>
+      <c r="F121" s="0">
+        <v>182</v>
+      </c>
+      <c r="G121" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="122">
+      <c r="A122" s="0">
+        <v>132</v>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>Generated the RCADS-25-CG-MR from RCADS-47-CG-MR and RCADS-25-CG-EN</t>
+        </is>
+      </c>
+      <c r="C122" s="0">
+        <v>51</v>
+      </c>
+      <c r="D122" s="1">
+        <v>45974</v>
+      </c>
+      <c r="E122" s="0">
+        <v>1</v>
+      </c>
+      <c r="F122" s="0">
+        <v>183</v>
+      </c>
+      <c r="G122" s="0">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
